--- a/Test_Cases_ECommerce_ Testing_Project.xlsx
+++ b/Test_Cases_ECommerce_ Testing_Project.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="309">
   <si>
     <t>TC_ID</t>
   </si>
@@ -77,7 +77,10 @@
     <t>User is redirected to product pages successfully</t>
   </si>
   <si>
-    <t>Not Executed</t>
+    <t>User redirected to product pages successfully</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>High</t>
@@ -98,6 +101,9 @@
     <t>Error Message displayed - Username and password doesnot match</t>
   </si>
   <si>
+    <t>Red Error appears</t>
+  </si>
+  <si>
     <t>TC_003</t>
   </si>
   <si>
@@ -122,6 +128,9 @@
     <t>Error Message: username Required</t>
   </si>
   <si>
+    <t>Error shows</t>
+  </si>
+  <si>
     <t>TC_005</t>
   </si>
   <si>
@@ -155,6 +164,9 @@
     <t>Error Message: Sorry this user has been locked out</t>
   </si>
   <si>
+    <t>locked out message shows</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -168,6 +180,9 @@
   </si>
   <si>
     <t>Error Message: Login should fail as username is case sensitive</t>
+  </si>
+  <si>
+    <t>Error appears</t>
   </si>
   <si>
     <t>TC_009</t>
@@ -232,6 +247,9 @@
     <t>Username field, Password field, Login Button and swag Labs logo all visible</t>
   </si>
   <si>
+    <t>All 4 UI elements are visible</t>
+  </si>
+  <si>
     <t>TC_011</t>
   </si>
   <si>
@@ -250,6 +268,9 @@
     <t>All 6 Products are visible with product name, price and image</t>
   </si>
   <si>
+    <t>Products Visible with Name, Price and Image</t>
+  </si>
+  <si>
     <t>TC_012</t>
   </si>
   <si>
@@ -265,6 +286,12 @@
     <t>All 6 product images load without any broken image icon</t>
   </si>
   <si>
+    <t>All 6 products showing same incorrect image icon instead of individual product images</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
     <t>TC_013</t>
   </si>
   <si>
@@ -277,6 +304,9 @@
     <t>Price is visible for all 6 products in $ format</t>
   </si>
   <si>
+    <t>All prices shows in $</t>
+  </si>
+  <si>
     <t>TC_014</t>
   </si>
   <si>
@@ -292,6 +322,9 @@
     <t>Products are arranged from lowest price to highest price</t>
   </si>
   <si>
+    <t>First product is cheapest, last is most expensive</t>
+  </si>
+  <si>
     <t>TC_015</t>
   </si>
   <si>
@@ -304,6 +337,9 @@
     <t>Products are arranged from highest price to lowest price</t>
   </si>
   <si>
+    <t>First product is most Expensive, last is cheapest</t>
+  </si>
+  <si>
     <t>TC_016</t>
   </si>
   <si>
@@ -316,6 +352,9 @@
     <t>Products are arranged in alphabetical order A to Z</t>
   </si>
   <si>
+    <t>Products in A to Z order</t>
+  </si>
+  <si>
     <t>TC_017</t>
   </si>
   <si>
@@ -328,6 +367,9 @@
     <t>Products are arranged in reverse alphabetical order Z to A</t>
   </si>
   <si>
+    <t>Products in Z to A order</t>
+  </si>
+  <si>
     <t>TC_018</t>
   </si>
   <si>
@@ -340,6 +382,9 @@
     <t>Product detail page opens with full product information</t>
   </si>
   <si>
+    <t>standard_user: Correct product detail page opens — Pass  problem_user: Clicking product image opens wrong product detail page — Bug logged KAN-5</t>
+  </si>
+  <si>
     <t>TC_019</t>
   </si>
   <si>
@@ -358,6 +403,9 @@
     <t>Correct product name is displayed on detail page</t>
   </si>
   <si>
+    <t>Correct product name displayed on detail page</t>
+  </si>
+  <si>
     <t>TC_020</t>
   </si>
   <si>
@@ -373,6 +421,9 @@
     <t>Correct price is displayed matching the listing page price</t>
   </si>
   <si>
+    <t>Correct price displayed matching listing page</t>
+  </si>
+  <si>
     <t>TC_021</t>
   </si>
   <si>
@@ -385,6 +436,9 @@
     <t>Product description text is visible and readable</t>
   </si>
   <si>
+    <t>Product description text visible and readable</t>
+  </si>
+  <si>
     <t>TC_022</t>
   </si>
   <si>
@@ -397,6 +451,9 @@
     <t>"Add to Cart" button is visible and clickable</t>
   </si>
   <si>
+    <t>standard_user: Add to Cart button visible and working correctly problem_user: Add to Cart button visible but NOT working — clicking has no effect</t>
+  </si>
+  <si>
     <t>TC_023</t>
   </si>
   <si>
@@ -409,6 +466,9 @@
     <t>User is taken back to the main products listing page</t>
   </si>
   <si>
+    <t>Back to Products button works correctly</t>
+  </si>
+  <si>
     <t>TC_024</t>
   </si>
   <si>
@@ -427,6 +487,9 @@
     <t>Cart icon shows count "1"</t>
   </si>
   <si>
+    <t>standard_user: Cart icon shows count 1 correctly problem_user: Add to Cart button not working on products listing page — cart count does not update</t>
+  </si>
+  <si>
     <t>TC_025</t>
   </si>
   <si>
@@ -439,6 +502,9 @@
     <t>Cart icon shows count "3"</t>
   </si>
   <si>
+    <t>Shows 3</t>
+  </si>
+  <si>
     <t>TC_026</t>
   </si>
   <si>
@@ -451,6 +517,9 @@
     <t>Button text changes from "Add to cart" to "Remove"</t>
   </si>
   <si>
+    <t>Shows Remove</t>
+  </si>
+  <si>
     <t>TC_027</t>
   </si>
   <si>
@@ -466,6 +535,9 @@
     <t>Item removed, cart count decreases by 1</t>
   </si>
   <si>
+    <t>Count decreases</t>
+  </si>
+  <si>
     <t>TC_028</t>
   </si>
   <si>
@@ -481,6 +553,9 @@
     <t>Cart page opens showing all added items</t>
   </si>
   <si>
+    <t>cart page opens</t>
+  </si>
+  <si>
     <t>TC_029</t>
   </si>
   <si>
@@ -499,6 +574,9 @@
     <t>Both added products are visible with correct names and prices</t>
   </si>
   <si>
+    <t>Both products visible with correct names and prices in cart</t>
+  </si>
+  <si>
     <t>TC_030</t>
   </si>
   <si>
@@ -511,6 +589,9 @@
     <t>Price in cart exactly matches price shown on products page</t>
   </si>
   <si>
+    <t>Price in cart exactly matches listing page price</t>
+  </si>
+  <si>
     <t>TC_031</t>
   </si>
   <si>
@@ -526,6 +607,9 @@
     <t>Item is removed from cart and cart updates immediately</t>
   </si>
   <si>
+    <t>Item removed from cart immediately after clicking Remove</t>
+  </si>
+  <si>
     <t>TC_032</t>
   </si>
   <si>
@@ -541,6 +625,9 @@
     <t>Cart page shows empty — no items listed</t>
   </si>
   <si>
+    <t>Cart shows empty after removing all items</t>
+  </si>
+  <si>
     <t>TC_033</t>
   </si>
   <si>
@@ -556,6 +643,9 @@
     <t>User is redirected back to products listing page</t>
   </si>
   <si>
+    <t>Continue Shopping button takes back to products page</t>
+  </si>
+  <si>
     <t>TC_034</t>
   </si>
   <si>
@@ -568,6 +658,9 @@
     <t>User is taken to Checkout Step 1 — information form page</t>
   </si>
   <si>
+    <t>Checkout button opens checkout form page successfully</t>
+  </si>
+  <si>
     <t>TC_035</t>
   </si>
   <si>
@@ -601,6 +694,9 @@
     <t>User moves to Checkout Step 2 — order summary page</t>
   </si>
   <si>
+    <t>User moved to order summary page successfully</t>
+  </si>
+  <si>
     <t>TC_037</t>
   </si>
   <si>
@@ -613,6 +709,9 @@
     <t>Error message — First Name is required</t>
   </si>
   <si>
+    <t>Error message displayed — First Name is required</t>
+  </si>
+  <si>
     <t>TC_038</t>
   </si>
   <si>
@@ -625,6 +724,9 @@
     <t>Error message — Last Name is required</t>
   </si>
   <si>
+    <t>Error message displayed — Last Name is required</t>
+  </si>
+  <si>
     <t>TC_039</t>
   </si>
   <si>
@@ -637,6 +739,9 @@
     <t>Error message — Postal Code is required</t>
   </si>
   <si>
+    <t>Error message displayed — Zip Code is required</t>
+  </si>
+  <si>
     <t>TC_040</t>
   </si>
   <si>
@@ -658,6 +763,9 @@
     <t>User is taken back to cart page</t>
   </si>
   <si>
+    <t>Cancel button takes user back to cart page</t>
+  </si>
+  <si>
     <t>TC_042</t>
   </si>
   <si>
@@ -688,6 +796,9 @@
     <t>Item total matches the sum of all added product prices</t>
   </si>
   <si>
+    <t>Item total displayed correctly matching product price</t>
+  </si>
+  <si>
     <t>TC_044</t>
   </si>
   <si>
@@ -703,6 +814,9 @@
     <t>Tax amount is displayed separately on summary page</t>
   </si>
   <si>
+    <t>Tax amount displayed separately on summary page</t>
+  </si>
+  <si>
     <t>TC_045</t>
   </si>
   <si>
@@ -715,6 +829,9 @@
     <t>Order confirmation page is displayed with success message</t>
   </si>
   <si>
+    <t>Order confirmation page displayed after clicking Finish</t>
+  </si>
+  <si>
     <t>TC_046</t>
   </si>
   <si>
@@ -730,6 +847,9 @@
     <t>Page shows Thank you for your order! message</t>
   </si>
   <si>
+    <t>Thank you for your order message displayed</t>
+  </si>
+  <si>
     <t>TC_047</t>
   </si>
   <si>
@@ -745,6 +865,9 @@
     <t>User is taken back to products listing page</t>
   </si>
   <si>
+    <t>Back Home button takes user back to products page</t>
+  </si>
+  <si>
     <t>TC_048</t>
   </si>
   <si>
@@ -757,6 +880,9 @@
     <t>User is taken back to cart page with items still present</t>
   </si>
   <si>
+    <t>Cancel button takes user back to cart with items</t>
+  </si>
+  <si>
     <t>TC_049</t>
   </si>
   <si>
@@ -775,6 +901,9 @@
     <t>User is redirected to login page and session ends</t>
   </si>
   <si>
+    <t>User redirected to login page after logout</t>
+  </si>
+  <si>
     <t>TC_050</t>
   </si>
   <si>
@@ -790,6 +919,9 @@
     <t>User is redirected back to login page</t>
   </si>
   <si>
+    <t>Browser back button stays on login page</t>
+  </si>
+  <si>
     <t>TC_051</t>
   </si>
   <si>
@@ -814,6 +946,9 @@
     <t>Cart is cleared and cart count shows 0</t>
   </si>
   <si>
+    <t>Cart cleared and count shows 0 after Reset App State</t>
+  </si>
+  <si>
     <t>TC_053</t>
   </si>
   <si>
@@ -827,6 +962,9 @@
   </si>
   <si>
     <t>Page title shows Products</t>
+  </si>
+  <si>
+    <t>Page title shows Products correctly</t>
   </si>
   <si>
     <t>TC_054</t>
@@ -907,7 +1045,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border/>
     <border>
       <left style="thick">
@@ -923,11 +1061,44 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -941,24 +1112,32 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1183,7 +1362,7 @@
     <col customWidth="1" min="4" max="4" width="45.0"/>
     <col customWidth="1" min="5" max="5" width="104.0"/>
     <col customWidth="1" min="6" max="6" width="68.13"/>
-    <col customWidth="1" min="7" max="7" width="46.75"/>
+    <col customWidth="1" min="7" max="7" width="77.25"/>
     <col customWidth="1" min="8" max="8" width="13.25"/>
     <col customWidth="1" min="9" max="9" width="8.88"/>
   </cols>
@@ -1253,1494 +1432,1604 @@
       <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="H4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="H5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="5"/>
       <c r="H6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>27</v>
+      <c r="C7" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="H7" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>31</v>
+      <c r="C8" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="5"/>
       <c r="H8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="H9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="H10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="5"/>
+        <v>54</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="H12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="H13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J13" s="7"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="3" t="s">
-        <v>15</v>
+        <v>66</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="9"/>
+      <c r="C15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="H15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="12"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="9"/>
+        <v>63</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>91</v>
+      </c>
       <c r="H18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
+      <c r="E19" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="9"/>
+        <v>63</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="H20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="9"/>
+        <v>63</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="H21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G22" s="9"/>
+        <v>108</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="H22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G23" s="9"/>
+        <v>108</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="H23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="9"/>
+        <v>108</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>124</v>
+      </c>
       <c r="H24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G25" s="9"/>
+      <c r="C25" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>129</v>
+      </c>
       <c r="H25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="G26" s="9"/>
+        <v>108</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>134</v>
+      </c>
       <c r="H26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G27" s="8"/>
+        <v>135</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>141</v>
+      </c>
       <c r="H27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>16</v>
+        <v>75</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="G28" s="8"/>
+        <v>142</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>146</v>
+      </c>
       <c r="H28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G29" s="8"/>
+        <v>147</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>151</v>
+      </c>
       <c r="H29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G30" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>157</v>
+      </c>
       <c r="H30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="D31" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="G31" s="8"/>
+      <c r="C31" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>163</v>
+      </c>
       <c r="H31" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G32" s="11"/>
+        <v>164</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>170</v>
+      </c>
       <c r="H32" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G33" s="11"/>
+        <v>171</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="H33" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="G34" s="11"/>
+        <v>176</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="H34" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="G35" s="11"/>
+        <v>182</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="H35" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="G36" s="11"/>
+        <v>188</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>193</v>
+      </c>
       <c r="H36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C37" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="G37" s="11"/>
+      <c r="C37" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="H37" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G38" s="11"/>
+        <v>199</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="H38" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G39" s="11"/>
+        <v>205</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="H39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G40" s="11"/>
+        <v>211</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="H40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G41" s="11"/>
+        <v>216</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="H41" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="G42" s="11"/>
+        <v>221</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="H42" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G43" s="11"/>
+        <v>226</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="H43" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="G44" s="11"/>
+        <v>229</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="H44" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D45" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="E45" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="G45" s="11"/>
+      <c r="C45" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="H45" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G46" s="11"/>
+        <v>239</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="H46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="G47" s="11"/>
+        <v>245</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="H47" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="G48" s="11"/>
+        <v>251</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>255</v>
+      </c>
       <c r="H48" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="G49" s="11"/>
+        <v>256</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="H49" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="G50" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="H50" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="G51" s="11"/>
+        <v>268</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="H51" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="G52" s="11"/>
+        <v>273</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="H52" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="G53" s="11"/>
+        <v>280</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="H53" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="G54" s="11"/>
+        <v>286</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>289</v>
+      </c>
       <c r="H54" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="G55" s="11"/>
+        <v>290</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="H55" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="G56" s="11"/>
+        <v>295</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="H56" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>50</v>
+        <v>16</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="G57" s="11"/>
+        <v>301</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="H57" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>50</v>
+        <v>16</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="G58" s="11"/>
+        <v>305</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>308</v>
+      </c>
       <c r="H58" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>50</v>
+        <v>16</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
